--- a/The Ultimate Budget.xlsx
+++ b/The Ultimate Budget.xlsx
@@ -352,9 +352,9 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1391,6 +1391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00404A36"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1656,6 +1657,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1672,7 +1674,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Mar 2024 — Budget vs Actual</t>
+          <t>Mar 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1732,14 +1734,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,3,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -1755,14 +1751,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,3,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -1778,14 +1768,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,3,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -1801,14 +1785,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,3,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -1824,14 +1802,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,3,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -1847,14 +1819,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,3,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -1870,14 +1836,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,3,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -1893,14 +1853,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,3,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -1908,19 +1862,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -1951,7 +1905,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -1974,7 +1928,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -1997,7 +1951,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -2020,7 +1974,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -2043,7 +1997,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -2066,7 +2020,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -2089,7 +2043,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -2112,7 +2066,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -2135,7 +2089,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -2158,7 +2112,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -2181,7 +2135,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -2204,7 +2158,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -2227,7 +2181,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -2250,7 +2204,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -2273,7 +2227,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -2296,7 +2250,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -2319,7 +2273,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -2342,7 +2296,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -2365,7 +2319,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -2388,7 +2342,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -2411,7 +2365,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -2434,7 +2388,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -2470,6 +2424,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2486,7 +2441,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Apr 2024 — Budget vs Actual</t>
+          <t>Apr 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2546,14 +2501,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,4,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -2569,14 +2518,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,4,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2592,14 +2535,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,4,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2615,14 +2552,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,4,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -2638,14 +2569,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,4,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -2661,14 +2586,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,4,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -2684,14 +2603,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,4,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -2707,14 +2620,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,4,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -2722,19 +2629,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -2765,7 +2672,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -2788,7 +2695,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -2811,7 +2718,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -2834,7 +2741,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -2857,7 +2764,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -2880,7 +2787,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -2903,7 +2810,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -2926,7 +2833,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -2949,7 +2856,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -2972,7 +2879,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -2995,7 +2902,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -3018,7 +2925,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -3041,7 +2948,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -3064,7 +2971,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -3087,7 +2994,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -3110,7 +3017,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -3133,7 +3040,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -3156,7 +3063,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -3179,7 +3086,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -3202,7 +3109,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -3225,7 +3132,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -3248,7 +3155,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -3284,6 +3191,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3300,7 +3208,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>May 2024 — Budget vs Actual</t>
+          <t>May 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3360,14 +3268,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,5,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -3383,14 +3285,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,5,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -3406,14 +3302,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,5,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -3429,14 +3319,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,5,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -3452,14 +3336,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,5,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -3475,14 +3353,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,5,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -3498,14 +3370,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,5,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -3521,14 +3387,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,5,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -3536,19 +3396,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -3579,7 +3439,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -3602,7 +3462,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -3625,7 +3485,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -3648,7 +3508,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -3671,7 +3531,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -3694,7 +3554,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -3717,7 +3577,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -3740,7 +3600,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -3763,7 +3623,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -3786,7 +3646,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -3809,7 +3669,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -3832,7 +3692,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -3855,7 +3715,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -3878,7 +3738,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -3901,7 +3761,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -3924,7 +3784,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -3947,7 +3807,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -3970,7 +3830,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -3993,7 +3853,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -4016,7 +3876,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -4039,7 +3899,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -4062,7 +3922,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -4098,6 +3958,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4114,7 +3975,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Jun 2024 — Budget vs Actual</t>
+          <t>Jun 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4174,14 +4035,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,6,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -4197,14 +4052,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,6,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -4220,14 +4069,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,6,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -4243,14 +4086,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,6,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -4266,14 +4103,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,6,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -4289,14 +4120,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,6,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -4312,14 +4137,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,6,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -4335,14 +4154,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,6,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -4350,19 +4163,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -4393,7 +4206,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -4416,7 +4229,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -4439,7 +4252,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -4462,7 +4275,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -4485,7 +4298,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -4508,7 +4321,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -4531,7 +4344,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -4554,7 +4367,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -4577,7 +4390,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -4600,7 +4413,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -4623,7 +4436,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -4646,7 +4459,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -4669,7 +4482,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -4692,7 +4505,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -4715,7 +4528,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -4738,7 +4551,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -4761,7 +4574,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -4784,7 +4597,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -4807,7 +4620,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -4830,7 +4643,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -4853,7 +4666,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -4876,7 +4689,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -4912,6 +4725,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4928,7 +4742,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Jul 2024 — Budget vs Actual</t>
+          <t>Jul 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4988,14 +4802,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,7,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -5011,14 +4819,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,7,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -5034,14 +4836,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,7,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -5057,14 +4853,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,7,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -5080,14 +4870,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,7,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -5103,14 +4887,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,7,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -5126,14 +4904,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,7,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -5149,14 +4921,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,7,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -5164,19 +4930,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -5207,7 +4973,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -5230,7 +4996,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -5253,7 +5019,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -5276,7 +5042,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -5299,7 +5065,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -5322,7 +5088,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -5345,7 +5111,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -5368,7 +5134,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -5391,7 +5157,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -5414,7 +5180,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -5437,7 +5203,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -5460,7 +5226,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -5483,7 +5249,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -5506,7 +5272,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -5529,7 +5295,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -5552,7 +5318,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -5575,7 +5341,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -5598,7 +5364,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -5621,7 +5387,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -5644,7 +5410,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -5667,7 +5433,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -5690,7 +5456,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -5726,6 +5492,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5742,7 +5509,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Aug 2024 — Budget vs Actual</t>
+          <t>Aug 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5802,14 +5569,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,8,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -5825,14 +5586,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,8,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -5848,14 +5603,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,8,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -5871,14 +5620,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,8,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -5894,14 +5637,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,8,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -5917,14 +5654,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,8,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -5940,14 +5671,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,8,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -5963,14 +5688,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,8,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -5978,19 +5697,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -6021,7 +5740,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -6044,7 +5763,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -6067,7 +5786,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -6090,7 +5809,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -6113,7 +5832,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -6136,7 +5855,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -6159,7 +5878,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -6182,7 +5901,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -6205,7 +5924,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -6228,7 +5947,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -6251,7 +5970,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -6274,7 +5993,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -6297,7 +6016,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -6320,7 +6039,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -6343,7 +6062,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -6366,7 +6085,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -6389,7 +6108,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -6412,7 +6131,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -6435,7 +6154,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -6458,7 +6177,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -6481,7 +6200,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -6504,7 +6223,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -6540,6 +6259,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6556,7 +6276,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Sep 2024 — Budget vs Actual</t>
+          <t>Sep 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6616,14 +6336,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,9,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -6639,14 +6353,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,9,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -6662,14 +6370,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,9,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -6685,14 +6387,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,9,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -6708,14 +6404,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,9,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -6731,14 +6421,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,9,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -6754,14 +6438,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,9,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -6777,14 +6455,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,9,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -6792,19 +6464,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -6835,7 +6507,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -6858,7 +6530,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -6881,7 +6553,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -6904,7 +6576,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -6927,7 +6599,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -6950,7 +6622,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -6973,7 +6645,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -6996,7 +6668,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -7019,7 +6691,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -7042,7 +6714,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -7065,7 +6737,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -7088,7 +6760,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -7111,7 +6783,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -7134,7 +6806,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -7157,7 +6829,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -7180,7 +6852,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -7203,7 +6875,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -7226,7 +6898,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -7249,7 +6921,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -7272,7 +6944,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -7295,7 +6967,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -7318,7 +6990,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -7354,6 +7026,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7370,7 +7043,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Oct 2024 — Budget vs Actual</t>
+          <t>Oct 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7430,14 +7103,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,10,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -7453,14 +7120,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,10,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -7476,14 +7137,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,10,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -7499,14 +7154,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,10,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -7522,14 +7171,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,10,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -7545,14 +7188,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,10,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -7568,14 +7205,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,10,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -7591,14 +7222,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,10,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -7606,19 +7231,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -7649,7 +7274,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -7672,7 +7297,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -7695,7 +7320,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -7718,7 +7343,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -7741,7 +7366,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -7764,7 +7389,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -7787,7 +7412,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -7810,7 +7435,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -7833,7 +7458,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -7856,7 +7481,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -7879,7 +7504,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -7902,7 +7527,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -7925,7 +7550,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -7948,7 +7573,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -7971,7 +7596,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -7994,7 +7619,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -8017,7 +7642,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -8040,7 +7665,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -8063,7 +7688,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -8086,7 +7711,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -8109,7 +7734,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -8132,7 +7757,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -8168,6 +7793,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8184,7 +7810,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Nov 2024 — Budget vs Actual</t>
+          <t>Nov 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8244,14 +7870,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,11,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -8267,14 +7887,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,11,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -8290,14 +7904,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,11,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -8313,14 +7921,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,11,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -8336,14 +7938,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,11,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -8359,14 +7955,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,11,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -8382,14 +7972,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,11,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -8405,14 +7989,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,11,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -8420,19 +7998,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -8463,7 +8041,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -8486,7 +8064,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -8509,7 +8087,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -8532,7 +8110,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -8555,7 +8133,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -8578,7 +8156,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -8601,7 +8179,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -8624,7 +8202,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -8647,7 +8225,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -8670,7 +8248,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -8693,7 +8271,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -8716,7 +8294,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -8739,7 +8317,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -8762,7 +8340,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -8785,7 +8363,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -8808,7 +8386,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -8831,7 +8409,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -8854,7 +8432,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -8877,7 +8455,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -8900,7 +8478,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -8923,7 +8501,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -8946,7 +8524,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -8982,6 +8560,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8998,7 +8577,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Dec 2024 — Budget vs Actual</t>
+          <t>Dec 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9058,14 +8637,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,12,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -9081,14 +8654,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,12,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -9104,14 +8671,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,12,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -9127,14 +8688,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,12,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -9150,14 +8705,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,12,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -9173,14 +8722,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,12,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -9196,14 +8739,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,12,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -9219,14 +8756,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,12,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -9234,19 +8765,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -9277,7 +8808,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -9300,7 +8831,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -9323,7 +8854,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -9346,7 +8877,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -9369,7 +8900,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -9392,7 +8923,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -9415,7 +8946,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -9438,7 +8969,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -9461,7 +8992,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -9484,7 +9015,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -9507,7 +9038,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -9530,7 +9061,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -9553,7 +9084,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -9576,7 +9107,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -9599,7 +9130,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -9622,7 +9153,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -9645,7 +9176,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -9668,7 +9199,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -9691,7 +9222,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -9714,7 +9245,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -9737,7 +9268,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -9760,7 +9291,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -9796,6 +9327,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00404A36"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9958,6 +9490,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -10696,20 +10229,22 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10725,6 +10260,7 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="59" t="inlineStr">
@@ -10734,35 +10270,40 @@
       </c>
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Original Balance</t>
         </is>
       </c>
       <c r="C2" s="59" t="inlineStr">
         <is>
+          <t>Current Balance</t>
+        </is>
+      </c>
+      <c r="D2" s="59" t="inlineStr">
+        <is>
           <t>APR (%)</t>
         </is>
       </c>
-      <c r="D2" s="59" t="inlineStr">
+      <c r="E2" s="59" t="inlineStr">
         <is>
           <t>Min Payment</t>
         </is>
       </c>
-      <c r="E2" s="59" t="inlineStr">
+      <c r="F2" s="59" t="inlineStr">
         <is>
           <t>Monthly Payment</t>
         </is>
       </c>
-      <c r="F2" s="59" t="inlineStr">
+      <c r="G2" s="59" t="inlineStr">
         <is>
           <t>Months to Payoff</t>
         </is>
       </c>
-      <c r="G2" s="59" t="inlineStr">
+      <c r="H2" s="59" t="inlineStr">
         <is>
           <t>Total Interest</t>
         </is>
       </c>
-      <c r="H2" s="59" t="inlineStr">
+      <c r="I2" s="59" t="inlineStr">
         <is>
           <t>% Paid Off</t>
         </is>
@@ -10775,27 +10316,31 @@
         </is>
       </c>
       <c r="B3" s="42" t="n">
+        <v>3800</v>
+      </c>
+      <c r="C3" s="42" t="n">
         <v>3500</v>
       </c>
-      <c r="C3" s="60" t="n">
+      <c r="D3" s="60" t="n">
         <v>19.99</v>
       </c>
-      <c r="D3" s="42" t="n">
+      <c r="E3" s="42" t="n">
         <v>70</v>
       </c>
-      <c r="E3" s="42" t="n">
+      <c r="F3" s="42" t="n">
         <v>150</v>
       </c>
-      <c r="F3" s="61">
-        <f>IF(OR(C3=0,E3=0),IF(E3=0,0,CEILING(B3/E3,1)),IFERROR(-NPER(C3/100/12,-E3,B3),0))</f>
-        <v/>
-      </c>
-      <c r="G3" s="48">
-        <f>IFERROR(MAX(0,F3*E3-B3),0)</f>
-        <v/>
-      </c>
-      <c r="H3" s="62" t="n">
-        <v>0</v>
+      <c r="G3" s="61">
+        <f>IF(OR(D3=0,F3=0),IF(F3=0,0,CEILING(C3/F3,1)),IFERROR(-NPER(D3/100/12,-F3,C3),0))</f>
+        <v/>
+      </c>
+      <c r="H3" s="48">
+        <f>IFERROR(MAX(0,G3*F3-C3),0)</f>
+        <v/>
+      </c>
+      <c r="I3" s="62">
+        <f>IF(B3=0,0,MAX(0,(B3-C3)/B3))</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -10805,27 +10350,31 @@
         </is>
       </c>
       <c r="B4" s="42" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C4" s="42" t="n">
         <v>12000</v>
       </c>
-      <c r="C4" s="60" t="n">
+      <c r="D4" s="60" t="n">
         <v>4.5</v>
       </c>
-      <c r="D4" s="42" t="n">
+      <c r="E4" s="42" t="n">
         <v>220</v>
       </c>
-      <c r="E4" s="42" t="n">
+      <c r="F4" s="42" t="n">
         <v>250</v>
       </c>
-      <c r="F4" s="61">
-        <f>IF(OR(C4=0,E4=0),IF(E4=0,0,CEILING(B4/E4,1)),IFERROR(-NPER(C4/100/12,-E4,B4),0))</f>
-        <v/>
-      </c>
-      <c r="G4" s="48">
-        <f>IFERROR(MAX(0,F4*E4-B4),0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="62" t="n">
-        <v>0</v>
+      <c r="G4" s="61">
+        <f>IF(OR(D4=0,F4=0),IF(F4=0,0,CEILING(C4/F4,1)),IFERROR(-NPER(D4/100/12,-F4,C4),0))</f>
+        <v/>
+      </c>
+      <c r="H4" s="48">
+        <f>IFERROR(MAX(0,G4*F4-C4),0)</f>
+        <v/>
+      </c>
+      <c r="I4" s="62">
+        <f>IF(B4=0,0,MAX(0,(B4-C4)/B4))</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -10835,27 +10384,31 @@
         </is>
       </c>
       <c r="B5" s="42" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C5" s="42" t="n">
         <v>25000</v>
       </c>
-      <c r="C5" s="60" t="n">
+      <c r="D5" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="42" t="n">
+      <c r="E5" s="42" t="n">
         <v>250</v>
       </c>
-      <c r="E5" s="42" t="n">
+      <c r="F5" s="42" t="n">
         <v>300</v>
       </c>
-      <c r="F5" s="61">
-        <f>IF(OR(C5=0,E5=0),IF(E5=0,0,CEILING(B5/E5,1)),IFERROR(-NPER(C5/100/12,-E5,B5),0))</f>
-        <v/>
-      </c>
-      <c r="G5" s="48">
-        <f>IFERROR(MAX(0,F5*E5-B5),0)</f>
-        <v/>
-      </c>
-      <c r="H5" s="62" t="n">
-        <v>0</v>
+      <c r="G5" s="61">
+        <f>IF(OR(D5=0,F5=0),IF(F5=0,0,CEILING(C5/F5,1)),IFERROR(-NPER(D5/100/12,-F5,C5),0))</f>
+        <v/>
+      </c>
+      <c r="H5" s="48">
+        <f>IFERROR(MAX(0,G5*F5-C5),0)</f>
+        <v/>
+      </c>
+      <c r="I5" s="62">
+        <f>IF(B5=0,0,MAX(0,(B5-C5)/B5))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -10865,27 +10418,31 @@
         </is>
       </c>
       <c r="B6" s="42" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C6" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="C6" s="60" t="n">
+      <c r="D6" s="60" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="E6" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="42" t="n">
+      <c r="F6" s="42" t="n">
         <v>150</v>
       </c>
-      <c r="F6" s="61">
-        <f>IF(OR(C6=0,E6=0),IF(E6=0,0,CEILING(B6/E6,1)),IFERROR(-NPER(C6/100/12,-E6,B6),0))</f>
-        <v/>
-      </c>
-      <c r="G6" s="48">
-        <f>IFERROR(MAX(0,F6*E6-B6),0)</f>
-        <v/>
-      </c>
-      <c r="H6" s="62" t="n">
-        <v>0</v>
+      <c r="G6" s="61">
+        <f>IF(OR(D6=0,F6=0),IF(F6=0,0,CEILING(C6/F6,1)),IFERROR(-NPER(D6/100/12,-F6,C6),0))</f>
+        <v/>
+      </c>
+      <c r="H6" s="48">
+        <f>IFERROR(MAX(0,G6*F6-C6),0)</f>
+        <v/>
+      </c>
+      <c r="I6" s="62">
+        <f>IF(B6=0,0,MAX(0,(B6-C6)/B6))</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -10895,40 +10452,143 @@
         </is>
       </c>
       <c r="B7" s="42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C7" s="42" t="n">
         <v>800</v>
       </c>
-      <c r="C7" s="60" t="n">
+      <c r="D7" s="60" t="n">
         <v>0</v>
-      </c>
-      <c r="D7" s="42" t="n">
-        <v>50</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="61">
-        <f>IF(OR(C7=0,E7=0),IF(E7=0,0,CEILING(B7/E7,1)),IFERROR(-NPER(C7/100/12,-E7,B7),0))</f>
-        <v/>
-      </c>
-      <c r="G7" s="48">
-        <f>IFERROR(MAX(0,F7*E7-B7),0)</f>
-        <v/>
-      </c>
-      <c r="H7" s="62" t="n">
-        <v>0</v>
+      <c r="F7" s="42" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="61">
+        <f>IF(OR(D7=0,F7=0),IF(F7=0,0,CEILING(C7/F7,1)),IFERROR(-NPER(D7/100/12,-F7,C7),0))</f>
+        <v/>
+      </c>
+      <c r="H7" s="48">
+        <f>IFERROR(MAX(0,G7*F7-C7),0)</f>
+        <v/>
+      </c>
+      <c r="I7" s="62">
+        <f>IF(B7=0,0,MAX(0,(B7-C7)/B7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr"/>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="62">
+        <f>IF(B8=0,0,MAX(0,(B8-C8)/B8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr"/>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="62">
+        <f>IF(B9=0,0,MAX(0,(B9-C9)/B9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="62">
+        <f>IF(B10=0,0,MAX(0,(B10-C10)/B10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="62">
+        <f>IF(B11=0,0,MAX(0,(B11-C11)/B11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="62">
+        <f>IF(B12=0,0,MAX(0,(B12-C12)/B12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="62">
+        <f>IF(B13=0,0,MAX(0,(B13-C13)/B13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="62">
+        <f>IF(B14=0,0,MAX(0,(B14-C14)/B14))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H3:H7">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
+  <conditionalFormatting sqref="I3:I14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="008B9A7A"/>
-      </dataBar>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF404A36"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10938,10 +10598,11 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11019,7 +10680,7 @@
         <f>B3-C3</f>
         <v/>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="52">
         <f>IF(B3=0,0,C3/B3)</f>
         <v/>
       </c>
@@ -11050,7 +10711,7 @@
         <f>B4-C4</f>
         <v/>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="52">
         <f>IF(B4=0,0,C4/B4)</f>
         <v/>
       </c>
@@ -11081,7 +10742,7 @@
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="52">
         <f>IF(B5=0,0,C5/B5)</f>
         <v/>
       </c>
@@ -11112,7 +10773,7 @@
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="52">
         <f>IF(B6=0,0,C6/B6)</f>
         <v/>
       </c>
@@ -11143,7 +10804,7 @@
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="52">
         <f>IF(B7=0,0,C7/B7)</f>
         <v/>
       </c>
@@ -11153,18 +10814,169 @@
         </is>
       </c>
       <c r="G7" s="35" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr"/>
+      <c r="B8" s="42" t="n"/>
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="48">
+        <f>IF(B8="","",B8-C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="52">
+        <f>IF(B8=0,0,C8/B8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="35" t="inlineStr"/>
+      <c r="G8" s="35" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr"/>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="48">
+        <f>IF(B9="","",B9-C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="52">
+        <f>IF(B9=0,0,C9/B9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="35" t="inlineStr"/>
+      <c r="G9" s="35" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="48">
+        <f>IF(B10="","",B10-C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="52">
+        <f>IF(B10=0,0,C10/B10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="35" t="inlineStr"/>
+      <c r="G10" s="35" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr"/>
+      <c r="B11" s="42" t="n"/>
+      <c r="C11" s="42" t="n"/>
+      <c r="D11" s="48">
+        <f>IF(B11="","",B11-C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="52">
+        <f>IF(B11=0,0,C11/B11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="35" t="inlineStr"/>
+      <c r="G11" s="35" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr"/>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="42" t="n"/>
+      <c r="D12" s="48">
+        <f>IF(B12="","",B12-C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="52">
+        <f>IF(B12=0,0,C12/B12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="35" t="inlineStr"/>
+      <c r="G12" s="35" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr"/>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="48">
+        <f>IF(B13="","",B13-C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="52">
+        <f>IF(B13=0,0,C13/B13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="35" t="inlineStr"/>
+      <c r="G13" s="35" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr"/>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="48">
+        <f>IF(B14="","",B14-C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="52">
+        <f>IF(B14=0,0,C14/B14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="35" t="inlineStr"/>
+      <c r="G14" s="35" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="48">
+        <f>IF(B15="","",B15-C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="52">
+        <f>IF(B15=0,0,C15/B15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="35" t="inlineStr"/>
+      <c r="G15" s="35" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="42" t="n"/>
+      <c r="D16" s="48">
+        <f>IF(B16="","",B16-C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="52">
+        <f>IF(B16=0,0,C16/B16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="35" t="inlineStr"/>
+      <c r="G16" s="35" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="48">
+        <f>IF(B17="","",B17-C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="52">
+        <f>IF(B17=0,0,C17/B17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="35" t="inlineStr"/>
+      <c r="G17" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3:E7">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
+  <conditionalFormatting sqref="E3:E17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="008B9A7A"/>
-      </dataBar>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF8B9A7A"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11174,10 +10986,11 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11240,7 +11053,7 @@
       <c r="D3" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="52">
         <f>IF(D3=0,0,C3/D3)</f>
         <v/>
       </c>
@@ -11260,7 +11073,7 @@
       <c r="D4" s="42" t="n">
         <v>3000</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="52">
         <f>IF(D4=0,0,C4/D4)</f>
         <v/>
       </c>
@@ -11280,7 +11093,7 @@
       <c r="D5" s="42" t="n">
         <v>6000</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="52">
         <f>IF(D5=0,0,C5/D5)</f>
         <v/>
       </c>
@@ -11300,8 +11113,118 @@
       <c r="D6" s="42" t="n">
         <v>2000</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="52">
         <f>IF(D6=0,0,C6/D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr"/>
+      <c r="B7" s="42" t="n"/>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="52">
+        <f>IF(D7=0,0,C7/D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr"/>
+      <c r="B8" s="42" t="n"/>
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="42" t="n"/>
+      <c r="E8" s="52">
+        <f>IF(D8=0,0,C8/D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr"/>
+      <c r="B9" s="42" t="n"/>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="42" t="n"/>
+      <c r="E9" s="52">
+        <f>IF(D9=0,0,C9/D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr"/>
+      <c r="B10" s="42" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="52">
+        <f>IF(D10=0,0,C10/D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr"/>
+      <c r="B11" s="42" t="n"/>
+      <c r="C11" s="42" t="n"/>
+      <c r="D11" s="42" t="n"/>
+      <c r="E11" s="52">
+        <f>IF(D11=0,0,C11/D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr"/>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="42" t="n"/>
+      <c r="D12" s="42" t="n"/>
+      <c r="E12" s="52">
+        <f>IF(D12=0,0,C12/D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr"/>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="52">
+        <f>IF(D13=0,0,C13/D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr"/>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="42" t="n"/>
+      <c r="E14" s="52">
+        <f>IF(D14=0,0,C14/D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="52">
+        <f>IF(D15=0,0,C15/D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="42" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="52">
+        <f>IF(D16=0,0,C16/D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="52">
+        <f>IF(D17=0,0,C17/D17)</f>
         <v/>
       </c>
     </row>
@@ -11309,13 +11232,14 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3:E6">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
+  <conditionalFormatting sqref="E3:E17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="008B9A7A"/>
-      </dataBar>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF8B9A7A"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11325,10 +11249,11 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11411,87 +11336,147 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr"/>
+      <c r="B8" s="42" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr"/>
+      <c r="B9" s="42" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr"/>
+      <c r="B10" s="42" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr"/>
+      <c r="B11" s="42" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr"/>
+      <c r="B12" s="42" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr"/>
+      <c r="B13" s="42" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr"/>
+      <c r="B14" s="42" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B8" s="51">
-        <f>SUM(B3:B7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="53" t="inlineStr">
+      <c r="B15" s="50">
+        <f>SUM(B3:B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="53" t="inlineStr">
         <is>
           <t>LIABILITIES</t>
         </is>
       </c>
-      <c r="B10" s="53" t="inlineStr">
+      <c r="B17" s="53" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="B11" s="42" t="n">
+      <c r="B18" s="42" t="n">
         <v>180000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>Car Loan</t>
         </is>
       </c>
-      <c r="B12" s="42" t="n">
+      <c r="B19" s="42" t="n">
         <v>12000</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>Credit Card</t>
         </is>
       </c>
-      <c r="B13" s="42" t="n">
+      <c r="B20" s="42" t="n">
         <v>3500</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>Student Loan</t>
         </is>
       </c>
-      <c r="B14" s="42" t="n">
+      <c r="B21" s="42" t="n">
         <v>25000</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="53" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr"/>
+      <c r="B22" s="42" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr"/>
+      <c r="B23" s="42" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="inlineStr"/>
+      <c r="B24" s="42" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="inlineStr"/>
+      <c r="B25" s="42" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr"/>
+      <c r="B26" s="42" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="inlineStr"/>
+      <c r="B27" s="42" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="inlineStr"/>
+      <c r="B28" s="42" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="inlineStr"/>
+      <c r="B29" s="42" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B15" s="54">
-        <f>SUM(B11:B14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="63" t="inlineStr">
+      <c r="B30" s="54">
+        <f>SUM(B18:B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="63" t="inlineStr">
         <is>
           <t>NET WORTH</t>
         </is>
       </c>
-      <c r="B17" s="64">
-        <f>B8-B15</f>
+      <c r="B32" s="64">
+        <f>B15-B30</f>
         <v/>
       </c>
     </row>
@@ -11506,10 +11491,11 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11797,17 +11783,149 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr"/>
+      <c r="B11" s="42" t="n"/>
+      <c r="C11" s="48">
+        <f>IF(B11="","",B11*12)</f>
+        <v/>
+      </c>
+      <c r="D11" s="35" t="inlineStr"/>
+      <c r="E11" s="35" t="inlineStr"/>
+      <c r="F11" s="38" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr"/>
+      <c r="B12" s="42" t="n"/>
+      <c r="C12" s="48">
+        <f>IF(B12="","",B12*12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="35" t="inlineStr"/>
+      <c r="E12" s="35" t="inlineStr"/>
+      <c r="F12" s="38" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr"/>
+      <c r="B13" s="42" t="n"/>
+      <c r="C13" s="48">
+        <f>IF(B13="","",B13*12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="35" t="inlineStr"/>
+      <c r="E13" s="35" t="inlineStr"/>
+      <c r="F13" s="38" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr"/>
+      <c r="B14" s="42" t="n"/>
+      <c r="C14" s="48">
+        <f>IF(B14="","",B14*12)</f>
+        <v/>
+      </c>
+      <c r="D14" s="35" t="inlineStr"/>
+      <c r="E14" s="35" t="inlineStr"/>
+      <c r="F14" s="38" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="48">
+        <f>IF(B15="","",B15*12)</f>
+        <v/>
+      </c>
+      <c r="D15" s="35" t="inlineStr"/>
+      <c r="E15" s="35" t="inlineStr"/>
+      <c r="F15" s="38" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="48">
+        <f>IF(B16="","",B16*12)</f>
+        <v/>
+      </c>
+      <c r="D16" s="35" t="inlineStr"/>
+      <c r="E16" s="35" t="inlineStr"/>
+      <c r="F16" s="38" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="48">
+        <f>IF(B17="","",B17*12)</f>
+        <v/>
+      </c>
+      <c r="D17" s="35" t="inlineStr"/>
+      <c r="E17" s="35" t="inlineStr"/>
+      <c r="F17" s="38" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="48">
+        <f>IF(B18="","",B18*12)</f>
+        <v/>
+      </c>
+      <c r="D18" s="35" t="inlineStr"/>
+      <c r="E18" s="35" t="inlineStr"/>
+      <c r="F18" s="38" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr"/>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="48">
+        <f>IF(B19="","",B19*12)</f>
+        <v/>
+      </c>
+      <c r="D19" s="35" t="inlineStr"/>
+      <c r="E19" s="35" t="inlineStr"/>
+      <c r="F19" s="38" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr"/>
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="48">
+        <f>IF(B20="","",B20*12)</f>
+        <v/>
+      </c>
+      <c r="D20" s="35" t="inlineStr"/>
+      <c r="E20" s="35" t="inlineStr"/>
+      <c r="F20" s="38" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="48">
+        <f>IF(B21="","",B21*12)</f>
+        <v/>
+      </c>
+      <c r="D21" s="35" t="inlineStr"/>
+      <c r="E21" s="35" t="inlineStr"/>
+      <c r="F21" s="38" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="48">
+        <f>IF(B22="","",B22*12)</f>
+        <v/>
+      </c>
+      <c r="D22" s="35" t="inlineStr"/>
+      <c r="E22" s="35" t="inlineStr"/>
+      <c r="F22" s="38" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
         <is>
           <t>Monthly Total</t>
         </is>
       </c>
-      <c r="B11" s="51">
-        <f>SUM(B3:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="51">
-        <f>SUM(C3:C10)</f>
+      <c r="B23" s="50">
+        <f>SUM(B3:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="50">
+        <f>SUM(C3:C22)</f>
         <v/>
       </c>
     </row>
@@ -11822,10 +11940,11 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12410,61 +12529,253 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr"/>
+      <c r="B11" s="47" t="inlineStr"/>
+      <c r="C11" s="47" t="inlineStr"/>
+      <c r="D11" s="47" t="inlineStr"/>
+      <c r="E11" s="47" t="inlineStr"/>
+      <c r="F11" s="47" t="inlineStr"/>
+      <c r="G11" s="47" t="inlineStr"/>
+      <c r="H11" s="47" t="inlineStr"/>
+      <c r="I11" s="47" t="inlineStr"/>
+      <c r="J11" s="47" t="inlineStr"/>
+      <c r="K11" s="47" t="inlineStr"/>
+      <c r="L11" s="47" t="inlineStr"/>
+      <c r="M11" s="47" t="inlineStr"/>
+      <c r="N11" s="48" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr"/>
+      <c r="B12" s="47" t="inlineStr"/>
+      <c r="C12" s="47" t="inlineStr"/>
+      <c r="D12" s="47" t="inlineStr"/>
+      <c r="E12" s="47" t="inlineStr"/>
+      <c r="F12" s="47" t="inlineStr"/>
+      <c r="G12" s="47" t="inlineStr"/>
+      <c r="H12" s="47" t="inlineStr"/>
+      <c r="I12" s="47" t="inlineStr"/>
+      <c r="J12" s="47" t="inlineStr"/>
+      <c r="K12" s="47" t="inlineStr"/>
+      <c r="L12" s="47" t="inlineStr"/>
+      <c r="M12" s="47" t="inlineStr"/>
+      <c r="N12" s="48" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr"/>
+      <c r="B13" s="47" t="inlineStr"/>
+      <c r="C13" s="47" t="inlineStr"/>
+      <c r="D13" s="47" t="inlineStr"/>
+      <c r="E13" s="47" t="inlineStr"/>
+      <c r="F13" s="47" t="inlineStr"/>
+      <c r="G13" s="47" t="inlineStr"/>
+      <c r="H13" s="47" t="inlineStr"/>
+      <c r="I13" s="47" t="inlineStr"/>
+      <c r="J13" s="47" t="inlineStr"/>
+      <c r="K13" s="47" t="inlineStr"/>
+      <c r="L13" s="47" t="inlineStr"/>
+      <c r="M13" s="47" t="inlineStr"/>
+      <c r="N13" s="48" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr"/>
+      <c r="B14" s="47" t="inlineStr"/>
+      <c r="C14" s="47" t="inlineStr"/>
+      <c r="D14" s="47" t="inlineStr"/>
+      <c r="E14" s="47" t="inlineStr"/>
+      <c r="F14" s="47" t="inlineStr"/>
+      <c r="G14" s="47" t="inlineStr"/>
+      <c r="H14" s="47" t="inlineStr"/>
+      <c r="I14" s="47" t="inlineStr"/>
+      <c r="J14" s="47" t="inlineStr"/>
+      <c r="K14" s="47" t="inlineStr"/>
+      <c r="L14" s="47" t="inlineStr"/>
+      <c r="M14" s="47" t="inlineStr"/>
+      <c r="N14" s="48" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr"/>
+      <c r="B15" s="47" t="inlineStr"/>
+      <c r="C15" s="47" t="inlineStr"/>
+      <c r="D15" s="47" t="inlineStr"/>
+      <c r="E15" s="47" t="inlineStr"/>
+      <c r="F15" s="47" t="inlineStr"/>
+      <c r="G15" s="47" t="inlineStr"/>
+      <c r="H15" s="47" t="inlineStr"/>
+      <c r="I15" s="47" t="inlineStr"/>
+      <c r="J15" s="47" t="inlineStr"/>
+      <c r="K15" s="47" t="inlineStr"/>
+      <c r="L15" s="47" t="inlineStr"/>
+      <c r="M15" s="47" t="inlineStr"/>
+      <c r="N15" s="48" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr"/>
+      <c r="B16" s="47" t="inlineStr"/>
+      <c r="C16" s="47" t="inlineStr"/>
+      <c r="D16" s="47" t="inlineStr"/>
+      <c r="E16" s="47" t="inlineStr"/>
+      <c r="F16" s="47" t="inlineStr"/>
+      <c r="G16" s="47" t="inlineStr"/>
+      <c r="H16" s="47" t="inlineStr"/>
+      <c r="I16" s="47" t="inlineStr"/>
+      <c r="J16" s="47" t="inlineStr"/>
+      <c r="K16" s="47" t="inlineStr"/>
+      <c r="L16" s="47" t="inlineStr"/>
+      <c r="M16" s="47" t="inlineStr"/>
+      <c r="N16" s="48" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr"/>
+      <c r="B17" s="47" t="inlineStr"/>
+      <c r="C17" s="47" t="inlineStr"/>
+      <c r="D17" s="47" t="inlineStr"/>
+      <c r="E17" s="47" t="inlineStr"/>
+      <c r="F17" s="47" t="inlineStr"/>
+      <c r="G17" s="47" t="inlineStr"/>
+      <c r="H17" s="47" t="inlineStr"/>
+      <c r="I17" s="47" t="inlineStr"/>
+      <c r="J17" s="47" t="inlineStr"/>
+      <c r="K17" s="47" t="inlineStr"/>
+      <c r="L17" s="47" t="inlineStr"/>
+      <c r="M17" s="47" t="inlineStr"/>
+      <c r="N17" s="48" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr"/>
+      <c r="B18" s="47" t="inlineStr"/>
+      <c r="C18" s="47" t="inlineStr"/>
+      <c r="D18" s="47" t="inlineStr"/>
+      <c r="E18" s="47" t="inlineStr"/>
+      <c r="F18" s="47" t="inlineStr"/>
+      <c r="G18" s="47" t="inlineStr"/>
+      <c r="H18" s="47" t="inlineStr"/>
+      <c r="I18" s="47" t="inlineStr"/>
+      <c r="J18" s="47" t="inlineStr"/>
+      <c r="K18" s="47" t="inlineStr"/>
+      <c r="L18" s="47" t="inlineStr"/>
+      <c r="M18" s="47" t="inlineStr"/>
+      <c r="N18" s="48" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr"/>
+      <c r="B19" s="47" t="inlineStr"/>
+      <c r="C19" s="47" t="inlineStr"/>
+      <c r="D19" s="47" t="inlineStr"/>
+      <c r="E19" s="47" t="inlineStr"/>
+      <c r="F19" s="47" t="inlineStr"/>
+      <c r="G19" s="47" t="inlineStr"/>
+      <c r="H19" s="47" t="inlineStr"/>
+      <c r="I19" s="47" t="inlineStr"/>
+      <c r="J19" s="47" t="inlineStr"/>
+      <c r="K19" s="47" t="inlineStr"/>
+      <c r="L19" s="47" t="inlineStr"/>
+      <c r="M19" s="47" t="inlineStr"/>
+      <c r="N19" s="48" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr"/>
+      <c r="B20" s="47" t="inlineStr"/>
+      <c r="C20" s="47" t="inlineStr"/>
+      <c r="D20" s="47" t="inlineStr"/>
+      <c r="E20" s="47" t="inlineStr"/>
+      <c r="F20" s="47" t="inlineStr"/>
+      <c r="G20" s="47" t="inlineStr"/>
+      <c r="H20" s="47" t="inlineStr"/>
+      <c r="I20" s="47" t="inlineStr"/>
+      <c r="J20" s="47" t="inlineStr"/>
+      <c r="K20" s="47" t="inlineStr"/>
+      <c r="L20" s="47" t="inlineStr"/>
+      <c r="M20" s="47" t="inlineStr"/>
+      <c r="N20" s="48" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr"/>
+      <c r="B21" s="47" t="inlineStr"/>
+      <c r="C21" s="47" t="inlineStr"/>
+      <c r="D21" s="47" t="inlineStr"/>
+      <c r="E21" s="47" t="inlineStr"/>
+      <c r="F21" s="47" t="inlineStr"/>
+      <c r="G21" s="47" t="inlineStr"/>
+      <c r="H21" s="47" t="inlineStr"/>
+      <c r="I21" s="47" t="inlineStr"/>
+      <c r="J21" s="47" t="inlineStr"/>
+      <c r="K21" s="47" t="inlineStr"/>
+      <c r="L21" s="47" t="inlineStr"/>
+      <c r="M21" s="47" t="inlineStr"/>
+      <c r="N21" s="48" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr"/>
+      <c r="B22" s="47" t="inlineStr"/>
+      <c r="C22" s="47" t="inlineStr"/>
+      <c r="D22" s="47" t="inlineStr"/>
+      <c r="E22" s="47" t="inlineStr"/>
+      <c r="F22" s="47" t="inlineStr"/>
+      <c r="G22" s="47" t="inlineStr"/>
+      <c r="H22" s="47" t="inlineStr"/>
+      <c r="I22" s="47" t="inlineStr"/>
+      <c r="J22" s="47" t="inlineStr"/>
+      <c r="K22" s="47" t="inlineStr"/>
+      <c r="L22" s="47" t="inlineStr"/>
+      <c r="M22" s="47" t="inlineStr"/>
+      <c r="N22" s="48" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
         <is>
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B11" s="51">
-        <f>SUM(B3:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="51">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="51">
-        <f>SUM(D3:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="51">
-        <f>SUM(E3:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="51">
-        <f>SUM(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="51">
-        <f>SUM(G3:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="51">
-        <f>SUM(H3:H10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="51">
-        <f>SUM(I3:I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="51">
-        <f>SUM(J3:J10)</f>
-        <v/>
-      </c>
-      <c r="K11" s="51">
-        <f>SUM(K3:K10)</f>
-        <v/>
-      </c>
-      <c r="L11" s="51">
-        <f>SUM(L3:L10)</f>
-        <v/>
-      </c>
-      <c r="M11" s="51">
-        <f>SUM(M3:M10)</f>
-        <v/>
-      </c>
-      <c r="N11" s="65">
-        <f>SUM(N3:N10)</f>
+      <c r="B23" s="50">
+        <f>SUM(B3:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="50">
+        <f>SUM(C3:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="50">
+        <f>SUM(D3:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="50">
+        <f>SUM(E3:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="50">
+        <f>SUM(F3:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="50">
+        <f>SUM(G3:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="50">
+        <f>SUM(H3:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="50">
+        <f>SUM(I3:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="50">
+        <f>SUM(J3:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="50">
+        <f>SUM(K3:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="50">
+        <f>SUM(L3:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="50">
+        <f>SUM(M3:M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="65">
+        <f>SUM(N3:N22)</f>
         <v/>
       </c>
     </row>
@@ -12479,6 +12790,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13042,15 +13354,15 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="51">
+      <c r="B25" s="50">
         <f>SUM(B3:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="51">
+      <c r="C25" s="50">
         <f>SUM(C3:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="50">
         <f>SUM(D3:D24)</f>
         <v/>
       </c>
@@ -13066,6 +13378,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13551,6 +13864,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -15600,20 +15914,20 @@
           <t>Monthly Budget Amounts</t>
         </is>
       </c>
-      <c r="B34" s="52" t="n"/>
-      <c r="C34" s="52" t="n"/>
-      <c r="D34" s="52" t="n"/>
-      <c r="E34" s="52" t="n"/>
-      <c r="F34" s="52" t="n"/>
-      <c r="G34" s="52" t="n"/>
-      <c r="H34" s="52" t="n"/>
-      <c r="I34" s="52" t="n"/>
-      <c r="J34" s="52" t="n"/>
-      <c r="K34" s="52" t="n"/>
-      <c r="L34" s="52" t="n"/>
-      <c r="M34" s="52" t="n"/>
-      <c r="N34" s="52" t="n"/>
-      <c r="O34" s="52" t="n"/>
+      <c r="B34" s="51" t="n"/>
+      <c r="C34" s="51" t="n"/>
+      <c r="D34" s="51" t="n"/>
+      <c r="E34" s="51" t="n"/>
+      <c r="F34" s="51" t="n"/>
+      <c r="G34" s="51" t="n"/>
+      <c r="H34" s="51" t="n"/>
+      <c r="I34" s="51" t="n"/>
+      <c r="J34" s="51" t="n"/>
+      <c r="K34" s="51" t="n"/>
+      <c r="L34" s="51" t="n"/>
+      <c r="M34" s="51" t="n"/>
+      <c r="N34" s="51" t="n"/>
+      <c r="O34" s="51" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="38" t="inlineStr">
@@ -17547,6 +17861,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00404A36"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -17667,6 +17982,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C0907E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -17920,6 +18236,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008B9A7A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -17947,7 +18264,7 @@
         </is>
       </c>
       <c r="B2" s="35" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="4">
@@ -18776,6 +19093,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008B9A7A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -18842,7 +19160,7 @@
     </row>
     <row r="2">
       <c r="A2" s="41" t="n">
-        <v>45296</v>
+        <v>46027</v>
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -18882,7 +19200,7 @@
     </row>
     <row r="3">
       <c r="A3" s="41" t="n">
-        <v>45301</v>
+        <v>46032</v>
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
@@ -18922,7 +19240,7 @@
     </row>
     <row r="4">
       <c r="A4" s="41" t="n">
-        <v>45303</v>
+        <v>46034</v>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
@@ -18962,7 +19280,7 @@
     </row>
     <row r="5">
       <c r="A5" s="41" t="n">
-        <v>45306</v>
+        <v>46037</v>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -19002,7 +19320,7 @@
     </row>
     <row r="6">
       <c r="A6" s="41" t="n">
-        <v>45311</v>
+        <v>46042</v>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
@@ -19042,7 +19360,7 @@
     </row>
     <row r="7">
       <c r="A7" s="41" t="n">
-        <v>45327</v>
+        <v>46058</v>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
@@ -19082,7 +19400,7 @@
     </row>
     <row r="8">
       <c r="A8" s="41" t="n">
-        <v>45330</v>
+        <v>46061</v>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
@@ -19122,7 +19440,7 @@
     </row>
     <row r="9">
       <c r="A9" s="41" t="n">
-        <v>45336</v>
+        <v>46067</v>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
@@ -19162,7 +19480,7 @@
     </row>
     <row r="10">
       <c r="A10" s="41" t="n">
-        <v>45340</v>
+        <v>46071</v>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -19202,7 +19520,7 @@
     </row>
     <row r="11">
       <c r="A11" s="41" t="n">
-        <v>45356</v>
+        <v>46086</v>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
@@ -19242,7 +19560,7 @@
     </row>
     <row r="12">
       <c r="A12" s="41" t="n">
-        <v>45358</v>
+        <v>46088</v>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -19282,7 +19600,7 @@
     </row>
     <row r="13">
       <c r="A13" s="41" t="n">
-        <v>45366</v>
+        <v>46096</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
@@ -31099,10 +31417,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008B9A7A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -31205,7 +31524,7 @@
       </c>
       <c r="H3" s="35" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
     </row>
@@ -31243,7 +31562,7 @@
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
     </row>
@@ -31281,7 +31600,7 @@
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2026-02-03</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31638,7 @@
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2026-02-10</t>
         </is>
       </c>
     </row>
@@ -31357,7 +31676,7 @@
       </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
     </row>
@@ -31395,7 +31714,7 @@
       </c>
       <c r="H8" s="35" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
@@ -31433,7 +31752,7 @@
       </c>
       <c r="H9" s="35" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2026-02-08</t>
         </is>
       </c>
     </row>
@@ -31471,7 +31790,7 @@
       </c>
       <c r="H10" s="35" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2026-02-12</t>
         </is>
       </c>
     </row>
@@ -31509,7 +31828,7 @@
       </c>
       <c r="H11" s="35" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
@@ -31547,9 +31866,159 @@
       </c>
       <c r="H12" s="35" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
-        </is>
-      </c>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr"/>
+      <c r="B13" s="35" t="inlineStr"/>
+      <c r="C13" s="35" t="inlineStr"/>
+      <c r="D13" s="35" t="inlineStr"/>
+      <c r="E13" s="35" t="inlineStr"/>
+      <c r="F13" s="35" t="inlineStr"/>
+      <c r="G13" s="38" t="inlineStr"/>
+      <c r="H13" s="35" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr"/>
+      <c r="B14" s="35" t="inlineStr"/>
+      <c r="C14" s="35" t="inlineStr"/>
+      <c r="D14" s="35" t="inlineStr"/>
+      <c r="E14" s="35" t="inlineStr"/>
+      <c r="F14" s="35" t="inlineStr"/>
+      <c r="G14" s="38" t="inlineStr"/>
+      <c r="H14" s="35" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr"/>
+      <c r="B15" s="35" t="inlineStr"/>
+      <c r="C15" s="35" t="inlineStr"/>
+      <c r="D15" s="35" t="inlineStr"/>
+      <c r="E15" s="35" t="inlineStr"/>
+      <c r="F15" s="35" t="inlineStr"/>
+      <c r="G15" s="38" t="inlineStr"/>
+      <c r="H15" s="35" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr"/>
+      <c r="B16" s="35" t="inlineStr"/>
+      <c r="C16" s="35" t="inlineStr"/>
+      <c r="D16" s="35" t="inlineStr"/>
+      <c r="E16" s="35" t="inlineStr"/>
+      <c r="F16" s="35" t="inlineStr"/>
+      <c r="G16" s="38" t="inlineStr"/>
+      <c r="H16" s="35" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr"/>
+      <c r="B17" s="35" t="inlineStr"/>
+      <c r="C17" s="35" t="inlineStr"/>
+      <c r="D17" s="35" t="inlineStr"/>
+      <c r="E17" s="35" t="inlineStr"/>
+      <c r="F17" s="35" t="inlineStr"/>
+      <c r="G17" s="38" t="inlineStr"/>
+      <c r="H17" s="35" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr"/>
+      <c r="B18" s="35" t="inlineStr"/>
+      <c r="C18" s="35" t="inlineStr"/>
+      <c r="D18" s="35" t="inlineStr"/>
+      <c r="E18" s="35" t="inlineStr"/>
+      <c r="F18" s="35" t="inlineStr"/>
+      <c r="G18" s="38" t="inlineStr"/>
+      <c r="H18" s="35" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr"/>
+      <c r="B19" s="35" t="inlineStr"/>
+      <c r="C19" s="35" t="inlineStr"/>
+      <c r="D19" s="35" t="inlineStr"/>
+      <c r="E19" s="35" t="inlineStr"/>
+      <c r="F19" s="35" t="inlineStr"/>
+      <c r="G19" s="38" t="inlineStr"/>
+      <c r="H19" s="35" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr"/>
+      <c r="B20" s="35" t="inlineStr"/>
+      <c r="C20" s="35" t="inlineStr"/>
+      <c r="D20" s="35" t="inlineStr"/>
+      <c r="E20" s="35" t="inlineStr"/>
+      <c r="F20" s="35" t="inlineStr"/>
+      <c r="G20" s="38" t="inlineStr"/>
+      <c r="H20" s="35" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr"/>
+      <c r="B21" s="35" t="inlineStr"/>
+      <c r="C21" s="35" t="inlineStr"/>
+      <c r="D21" s="35" t="inlineStr"/>
+      <c r="E21" s="35" t="inlineStr"/>
+      <c r="F21" s="35" t="inlineStr"/>
+      <c r="G21" s="38" t="inlineStr"/>
+      <c r="H21" s="35" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr"/>
+      <c r="B22" s="35" t="inlineStr"/>
+      <c r="C22" s="35" t="inlineStr"/>
+      <c r="D22" s="35" t="inlineStr"/>
+      <c r="E22" s="35" t="inlineStr"/>
+      <c r="F22" s="35" t="inlineStr"/>
+      <c r="G22" s="38" t="inlineStr"/>
+      <c r="H22" s="35" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr"/>
+      <c r="B23" s="35" t="inlineStr"/>
+      <c r="C23" s="35" t="inlineStr"/>
+      <c r="D23" s="35" t="inlineStr"/>
+      <c r="E23" s="35" t="inlineStr"/>
+      <c r="F23" s="35" t="inlineStr"/>
+      <c r="G23" s="38" t="inlineStr"/>
+      <c r="H23" s="35" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="inlineStr"/>
+      <c r="B24" s="35" t="inlineStr"/>
+      <c r="C24" s="35" t="inlineStr"/>
+      <c r="D24" s="35" t="inlineStr"/>
+      <c r="E24" s="35" t="inlineStr"/>
+      <c r="F24" s="35" t="inlineStr"/>
+      <c r="G24" s="38" t="inlineStr"/>
+      <c r="H24" s="35" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="inlineStr"/>
+      <c r="B25" s="35" t="inlineStr"/>
+      <c r="C25" s="35" t="inlineStr"/>
+      <c r="D25" s="35" t="inlineStr"/>
+      <c r="E25" s="35" t="inlineStr"/>
+      <c r="F25" s="35" t="inlineStr"/>
+      <c r="G25" s="38" t="inlineStr"/>
+      <c r="H25" s="35" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr"/>
+      <c r="B26" s="35" t="inlineStr"/>
+      <c r="C26" s="35" t="inlineStr"/>
+      <c r="D26" s="35" t="inlineStr"/>
+      <c r="E26" s="35" t="inlineStr"/>
+      <c r="F26" s="35" t="inlineStr"/>
+      <c r="G26" s="38" t="inlineStr"/>
+      <c r="H26" s="35" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="inlineStr"/>
+      <c r="B27" s="35" t="inlineStr"/>
+      <c r="C27" s="35" t="inlineStr"/>
+      <c r="D27" s="35" t="inlineStr"/>
+      <c r="E27" s="35" t="inlineStr"/>
+      <c r="F27" s="35" t="inlineStr"/>
+      <c r="G27" s="38" t="inlineStr"/>
+      <c r="H27" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -31578,6 +32047,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008B9A7A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -33800,6 +34270,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -33816,7 +34287,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Jan 2024 — Budget vs Actual</t>
+          <t>Jan 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -33876,14 +34347,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,1,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -33899,14 +34364,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,1,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -33922,14 +34381,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,1,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -33945,14 +34398,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,1,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -33968,14 +34415,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,1,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -33991,14 +34432,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,1,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -34014,14 +34449,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,1,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -34037,14 +34466,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,1,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -34052,19 +34475,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -34095,7 +34518,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -34118,7 +34541,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -34141,7 +34564,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -34164,7 +34587,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -34187,7 +34610,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -34210,7 +34633,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -34233,7 +34656,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -34256,7 +34679,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -34279,7 +34702,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -34302,7 +34725,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -34325,7 +34748,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -34348,7 +34771,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -34371,7 +34794,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -34394,7 +34817,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -34417,7 +34840,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -34440,7 +34863,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -34463,7 +34886,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -34486,7 +34909,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -34509,7 +34932,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -34532,7 +34955,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -34555,7 +34978,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -34578,7 +35001,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>
@@ -34614,6 +35037,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9D2BB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -34630,7 +35054,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>Feb 2024 — Budget vs Actual</t>
+          <t>Feb 2026 — Budget vs Actual</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -34690,14 +35114,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,2,Transactions!$C$2:$C$601,A4),0)</f>
         <v/>
       </c>
-      <c r="D4" s="47">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IF(B4=0,0,C4/B4)</f>
-        <v/>
-      </c>
+      <c r="D4" s="18" t="inlineStr"/>
+      <c r="E4" s="18" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
@@ -34713,14 +35131,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,2,Transactions!$C$2:$C$601,A5),0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="50">
-        <f>IF(B5=0,0,C5/B5)</f>
-        <v/>
-      </c>
+      <c r="D5" s="18" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -34736,14 +35148,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,2,Transactions!$C$2:$C$601,A6),0)</f>
         <v/>
       </c>
-      <c r="D6" s="47">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="50">
-        <f>IF(B6=0,0,C6/B6)</f>
-        <v/>
-      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -34759,14 +35165,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,2,Transactions!$C$2:$C$601,A7),0)</f>
         <v/>
       </c>
-      <c r="D7" s="47">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="50">
-        <f>IF(B7=0,0,C7/B7)</f>
-        <v/>
-      </c>
+      <c r="D7" s="18" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -34782,14 +35182,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,2,Transactions!$C$2:$C$601,A8),0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="50">
-        <f>IF(B8=0,0,C8/B8)</f>
-        <v/>
-      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -34805,14 +35199,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,2,Transactions!$C$2:$C$601,A9),0)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="50">
-        <f>IF(B9=0,0,C9/B9)</f>
-        <v/>
-      </c>
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -34828,14 +35216,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,2,Transactions!$C$2:$C$601,A10),0)</f>
         <v/>
       </c>
-      <c r="D10" s="47">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="50">
-        <f>IF(B10=0,0,C10/B10)</f>
-        <v/>
-      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+      <c r="E10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -34851,14 +35233,8 @@
         <f>IFERROR(SUMIFS(Transactions!$F$2:$F$601,Transactions!$H$2:$H$601,Settings!$B$2,Transactions!$G$2:$G$601,2,Transactions!$C$2:$C$601,A11),0)</f>
         <v/>
       </c>
-      <c r="D11" s="47">
-        <f>B11-C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="50">
-        <f>IF(B11=0,0,C11/B11)</f>
-        <v/>
-      </c>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="45" t="inlineStr">
@@ -34866,19 +35242,19 @@
           <t>Total Income</t>
         </is>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="50">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr"/>
+      <c r="E12" s="51" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
@@ -34909,7 +35285,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="52">
         <f>IF(B15=0,0,C15/B15)</f>
         <v/>
       </c>
@@ -34932,7 +35308,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="52">
         <f>IF(B16=0,0,C16/B16)</f>
         <v/>
       </c>
@@ -34955,7 +35331,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="52">
         <f>IF(B17=0,0,C17/B17)</f>
         <v/>
       </c>
@@ -34978,7 +35354,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>IF(B18=0,0,C18/B18)</f>
         <v/>
       </c>
@@ -35001,7 +35377,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="52">
         <f>IF(B19=0,0,C19/B19)</f>
         <v/>
       </c>
@@ -35024,7 +35400,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="52">
         <f>IF(B20=0,0,C20/B20)</f>
         <v/>
       </c>
@@ -35047,7 +35423,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="52">
         <f>IF(B21=0,0,C21/B21)</f>
         <v/>
       </c>
@@ -35070,7 +35446,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="52">
         <f>IF(B22=0,0,C22/B22)</f>
         <v/>
       </c>
@@ -35093,7 +35469,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="52">
         <f>IF(B23=0,0,C23/B23)</f>
         <v/>
       </c>
@@ -35116,7 +35492,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="52">
         <f>IF(B24=0,0,C24/B24)</f>
         <v/>
       </c>
@@ -35139,7 +35515,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="52">
         <f>IF(B25=0,0,C25/B25)</f>
         <v/>
       </c>
@@ -35162,7 +35538,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="52">
         <f>IF(B26=0,0,C26/B26)</f>
         <v/>
       </c>
@@ -35185,7 +35561,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="52">
         <f>IF(B27=0,0,C27/B27)</f>
         <v/>
       </c>
@@ -35208,7 +35584,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="52">
         <f>IF(B28=0,0,C28/B28)</f>
         <v/>
       </c>
@@ -35231,7 +35607,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="52">
         <f>IF(B29=0,0,C29/B29)</f>
         <v/>
       </c>
@@ -35254,7 +35630,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="52">
         <f>IF(B30=0,0,C30/B30)</f>
         <v/>
       </c>
@@ -35277,7 +35653,7 @@
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="52">
         <f>IF(B31=0,0,C31/B31)</f>
         <v/>
       </c>
@@ -35300,7 +35676,7 @@
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="52">
         <f>IF(B32=0,0,C32/B32)</f>
         <v/>
       </c>
@@ -35323,7 +35699,7 @@
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="52">
         <f>IF(B33=0,0,C33/B33)</f>
         <v/>
       </c>
@@ -35346,7 +35722,7 @@
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="52">
         <f>IF(B34=0,0,C34/B34)</f>
         <v/>
       </c>
@@ -35369,7 +35745,7 @@
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="50">
+      <c r="E35" s="52">
         <f>IF(B35=0,0,C35/B35)</f>
         <v/>
       </c>
@@ -35392,7 +35768,7 @@
         <f>B36-C36</f>
         <v/>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="52">
         <f>IF(B36=0,0,C36/B36)</f>
         <v/>
       </c>

--- a/The Ultimate Budget.xlsx
+++ b/The Ultimate Budget.xlsx
@@ -247,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -369,6 +369,8 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="14" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -10331,7 +10333,7 @@
         <v>150</v>
       </c>
       <c r="G3" s="61">
-        <f>IF(OR(D3=0,F3=0),IF(F3=0,0,CEILING(C3/F3,1)),IFERROR(-NPER(D3/100/12,-F3,C3),0))</f>
+        <f>IF(OR(D3=0,F3=0),IF(F3=0,0,CEILING(C3/F3,1)),IFERROR(NPER(D3/100/12,-F3,C3),0))</f>
         <v/>
       </c>
       <c r="H3" s="48">
@@ -10365,7 +10367,7 @@
         <v>250</v>
       </c>
       <c r="G4" s="61">
-        <f>IF(OR(D4=0,F4=0),IF(F4=0,0,CEILING(C4/F4,1)),IFERROR(-NPER(D4/100/12,-F4,C4),0))</f>
+        <f>IF(OR(D4=0,F4=0),IF(F4=0,0,CEILING(C4/F4,1)),IFERROR(NPER(D4/100/12,-F4,C4),0))</f>
         <v/>
       </c>
       <c r="H4" s="48">
@@ -10399,7 +10401,7 @@
         <v>300</v>
       </c>
       <c r="G5" s="61">
-        <f>IF(OR(D5=0,F5=0),IF(F5=0,0,CEILING(C5/F5,1)),IFERROR(-NPER(D5/100/12,-F5,C5),0))</f>
+        <f>IF(OR(D5=0,F5=0),IF(F5=0,0,CEILING(C5/F5,1)),IFERROR(NPER(D5/100/12,-F5,C5),0))</f>
         <v/>
       </c>
       <c r="H5" s="48">
@@ -10433,7 +10435,7 @@
         <v>150</v>
       </c>
       <c r="G6" s="61">
-        <f>IF(OR(D6=0,F6=0),IF(F6=0,0,CEILING(C6/F6,1)),IFERROR(-NPER(D6/100/12,-F6,C6),0))</f>
+        <f>IF(OR(D6=0,F6=0),IF(F6=0,0,CEILING(C6/F6,1)),IFERROR(NPER(D6/100/12,-F6,C6),0))</f>
         <v/>
       </c>
       <c r="H6" s="48">
@@ -10467,7 +10469,7 @@
         <v>50</v>
       </c>
       <c r="G7" s="61">
-        <f>IF(OR(D7=0,F7=0),IF(F7=0,0,CEILING(C7/F7,1)),IFERROR(-NPER(D7/100/12,-F7,C7),0))</f>
+        <f>IF(OR(D7=0,F7=0),IF(F7=0,0,CEILING(C7/F7,1)),IFERROR(NPER(D7/100/12,-F7,C7),0))</f>
         <v/>
       </c>
       <c r="H7" s="48">
@@ -10480,98 +10482,140 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr"/>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="63" t="n"/>
+      <c r="C8" s="63" t="n"/>
+      <c r="D8" s="64" t="n"/>
+      <c r="E8" s="63" t="n"/>
+      <c r="F8" s="63" t="n"/>
+      <c r="G8" s="61">
+        <f>IF(OR(D8=0,F8=0),IF(F8=0,0,CEILING(C8/F8,1)),IFERROR(NPER(D8/100/12,-F8,C8),0))</f>
+        <v/>
+      </c>
+      <c r="H8" s="48">
+        <f>IFERROR(MAX(0,G8*F8-C8),0)</f>
+        <v/>
+      </c>
       <c r="I8" s="62">
         <f>IF(B8=0,0,MAX(0,(B8-C8)/B8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr"/>
-      <c r="B9" s="20" t="n"/>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="63" t="n"/>
+      <c r="C9" s="63" t="n"/>
+      <c r="D9" s="64" t="n"/>
+      <c r="E9" s="63" t="n"/>
+      <c r="F9" s="63" t="n"/>
+      <c r="G9" s="61">
+        <f>IF(OR(D9=0,F9=0),IF(F9=0,0,CEILING(C9/F9,1)),IFERROR(NPER(D9/100/12,-F9,C9),0))</f>
+        <v/>
+      </c>
+      <c r="H9" s="48">
+        <f>IFERROR(MAX(0,G9*F9-C9),0)</f>
+        <v/>
+      </c>
       <c r="I9" s="62">
         <f>IF(B9=0,0,MAX(0,(B9-C9)/B9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr"/>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="63" t="n"/>
+      <c r="C10" s="63" t="n"/>
+      <c r="D10" s="64" t="n"/>
+      <c r="E10" s="63" t="n"/>
+      <c r="F10" s="63" t="n"/>
+      <c r="G10" s="61">
+        <f>IF(OR(D10=0,F10=0),IF(F10=0,0,CEILING(C10/F10,1)),IFERROR(NPER(D10/100/12,-F10,C10),0))</f>
+        <v/>
+      </c>
+      <c r="H10" s="48">
+        <f>IFERROR(MAX(0,G10*F10-C10),0)</f>
+        <v/>
+      </c>
       <c r="I10" s="62">
         <f>IF(B10=0,0,MAX(0,(B10-C10)/B10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr"/>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="n"/>
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="63" t="n"/>
+      <c r="C11" s="63" t="n"/>
+      <c r="D11" s="64" t="n"/>
+      <c r="E11" s="63" t="n"/>
+      <c r="F11" s="63" t="n"/>
+      <c r="G11" s="61">
+        <f>IF(OR(D11=0,F11=0),IF(F11=0,0,CEILING(C11/F11,1)),IFERROR(NPER(D11/100/12,-F11,C11),0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="48">
+        <f>IFERROR(MAX(0,G11*F11-C11),0)</f>
+        <v/>
+      </c>
       <c r="I11" s="62">
         <f>IF(B11=0,0,MAX(0,(B11-C11)/B11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr"/>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="63" t="n"/>
+      <c r="C12" s="63" t="n"/>
+      <c r="D12" s="64" t="n"/>
+      <c r="E12" s="63" t="n"/>
+      <c r="F12" s="63" t="n"/>
+      <c r="G12" s="61">
+        <f>IF(OR(D12=0,F12=0),IF(F12=0,0,CEILING(C12/F12,1)),IFERROR(NPER(D12/100/12,-F12,C12),0))</f>
+        <v/>
+      </c>
+      <c r="H12" s="48">
+        <f>IFERROR(MAX(0,G12*F12-C12),0)</f>
+        <v/>
+      </c>
       <c r="I12" s="62">
         <f>IF(B12=0,0,MAX(0,(B12-C12)/B12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="14" t="n"/>
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="63" t="n"/>
+      <c r="C13" s="63" t="n"/>
+      <c r="D13" s="64" t="n"/>
+      <c r="E13" s="63" t="n"/>
+      <c r="F13" s="63" t="n"/>
+      <c r="G13" s="61">
+        <f>IF(OR(D13=0,F13=0),IF(F13=0,0,CEILING(C13/F13,1)),IFERROR(NPER(D13/100/12,-F13,C13),0))</f>
+        <v/>
+      </c>
+      <c r="H13" s="48">
+        <f>IFERROR(MAX(0,G13*F13-C13),0)</f>
+        <v/>
+      </c>
       <c r="I13" s="62">
         <f>IF(B13=0,0,MAX(0,(B13-C13)/B13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr"/>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="63" t="n"/>
+      <c r="C14" s="63" t="n"/>
+      <c r="D14" s="64" t="n"/>
+      <c r="E14" s="63" t="n"/>
+      <c r="F14" s="63" t="n"/>
+      <c r="G14" s="61">
+        <f>IF(OR(D14=0,F14=0),IF(F14=0,0,CEILING(C14/F14,1)),IFERROR(NPER(D14/100/12,-F14,C14),0))</f>
+        <v/>
+      </c>
+      <c r="H14" s="48">
+        <f>IFERROR(MAX(0,G14*F14-C14),0)</f>
+        <v/>
+      </c>
       <c r="I14" s="62">
         <f>IF(B14=0,0,MAX(0,(B14-C14)/B14))</f>
         <v/>
@@ -11470,12 +11514,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="63" t="inlineStr">
+      <c r="A32" s="65" t="inlineStr">
         <is>
           <t>NET WORTH</t>
         </is>
       </c>
-      <c r="B32" s="64">
+      <c r="B32" s="66">
         <f>B15-B30</f>
         <v/>
       </c>
@@ -12774,7 +12818,7 @@
         <f>SUM(M3:M22)</f>
         <v/>
       </c>
-      <c r="N23" s="65">
+      <c r="N23" s="67">
         <f>SUM(N3:N22)</f>
         <v/>
       </c>
@@ -12860,7 +12904,7 @@
         <f>B3-C3</f>
         <v/>
       </c>
-      <c r="E3" s="66">
+      <c r="E3" s="68">
         <f>IF(SUM(C3:C24)=0,0,C3/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -12883,7 +12927,7 @@
         <f>B4-C4</f>
         <v/>
       </c>
-      <c r="E4" s="66">
+      <c r="E4" s="68">
         <f>IF(SUM(C3:C24)=0,0,C4/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -12906,7 +12950,7 @@
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="68">
         <f>IF(SUM(C3:C24)=0,0,C5/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -12929,7 +12973,7 @@
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="66">
+      <c r="E6" s="68">
         <f>IF(SUM(C3:C24)=0,0,C6/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -12952,7 +12996,7 @@
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="66">
+      <c r="E7" s="68">
         <f>IF(SUM(C3:C24)=0,0,C7/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -12975,7 +13019,7 @@
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="66">
+      <c r="E8" s="68">
         <f>IF(SUM(C3:C24)=0,0,C8/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -12998,7 +13042,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="66">
+      <c r="E9" s="68">
         <f>IF(SUM(C3:C24)=0,0,C9/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13021,7 +13065,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="66">
+      <c r="E10" s="68">
         <f>IF(SUM(C3:C24)=0,0,C10/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13044,7 +13088,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="66">
+      <c r="E11" s="68">
         <f>IF(SUM(C3:C24)=0,0,C11/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13067,7 +13111,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="66">
+      <c r="E12" s="68">
         <f>IF(SUM(C3:C24)=0,0,C12/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13090,7 +13134,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="66">
+      <c r="E13" s="68">
         <f>IF(SUM(C3:C24)=0,0,C13/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13113,7 +13157,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="66">
+      <c r="E14" s="68">
         <f>IF(SUM(C3:C24)=0,0,C14/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13136,7 +13180,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="66">
+      <c r="E15" s="68">
         <f>IF(SUM(C3:C24)=0,0,C15/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13159,7 +13203,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="66">
+      <c r="E16" s="68">
         <f>IF(SUM(C3:C24)=0,0,C16/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13182,7 +13226,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="66">
+      <c r="E17" s="68">
         <f>IF(SUM(C3:C24)=0,0,C17/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13205,7 +13249,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="66">
+      <c r="E18" s="68">
         <f>IF(SUM(C3:C24)=0,0,C18/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13228,7 +13272,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="66">
+      <c r="E19" s="68">
         <f>IF(SUM(C3:C24)=0,0,C19/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13251,7 +13295,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="68">
         <f>IF(SUM(C3:C24)=0,0,C20/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13274,7 +13318,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="66">
+      <c r="E21" s="68">
         <f>IF(SUM(C3:C24)=0,0,C21/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13297,7 +13341,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="66">
+      <c r="E22" s="68">
         <f>IF(SUM(C3:C24)=0,0,C22/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13320,7 +13364,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="66">
+      <c r="E23" s="68">
         <f>IF(SUM(C3:C24)=0,0,C23/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13343,7 +13387,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="66">
+      <c r="E24" s="68">
         <f>IF(SUM(C3:C24)=0,0,C24/SUM(C$3:C$24))</f>
         <v/>
       </c>
@@ -13455,25 +13499,25 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="67" t="n">
+      <c r="A5" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="67" t="n">
+      <c r="B5" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="67" t="n">
+      <c r="C5" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="67" t="n">
+      <c r="D5" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="67" t="n">
+      <c r="E5" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="67" t="n">
+      <c r="F5" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="67" t="n">
+      <c r="G5" s="69" t="n">
         <v>7</v>
       </c>
       <c r="J5" s="57">
@@ -13506,25 +13550,25 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="67" t="n">
+      <c r="A6" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="67" t="n">
+      <c r="B6" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="67" t="n">
+      <c r="C6" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="67" t="n">
+      <c r="D6" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="67" t="n">
+      <c r="E6" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="67" t="n">
+      <c r="F6" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="G6" s="67" t="n">
+      <c r="G6" s="69" t="n">
         <v>14</v>
       </c>
       <c r="J6" s="57">
@@ -13557,25 +13601,25 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="67" t="n">
+      <c r="A7" s="69" t="n">
         <v>15</v>
       </c>
-      <c r="B7" s="67" t="n">
+      <c r="B7" s="69" t="n">
         <v>16</v>
       </c>
-      <c r="C7" s="67" t="n">
+      <c r="C7" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="D7" s="67" t="n">
+      <c r="D7" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="E7" s="67" t="n">
+      <c r="E7" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="F7" s="67" t="n">
+      <c r="F7" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="G7" s="67" t="n">
+      <c r="G7" s="69" t="n">
         <v>21</v>
       </c>
       <c r="J7" s="57">
@@ -13608,25 +13652,25 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="67" t="n">
+      <c r="A8" s="69" t="n">
         <v>22</v>
       </c>
-      <c r="B8" s="67" t="n">
+      <c r="B8" s="69" t="n">
         <v>23</v>
       </c>
-      <c r="C8" s="67" t="n">
+      <c r="C8" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="D8" s="67" t="n">
+      <c r="D8" s="69" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="67" t="n">
+      <c r="E8" s="69" t="n">
         <v>26</v>
       </c>
-      <c r="F8" s="67" t="n">
+      <c r="F8" s="69" t="n">
         <v>27</v>
       </c>
-      <c r="G8" s="67" t="n">
+      <c r="G8" s="69" t="n">
         <v>28</v>
       </c>
       <c r="J8" s="57">
@@ -13659,13 +13703,13 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="67" t="n">
+      <c r="A9" s="69" t="n">
         <v>29</v>
       </c>
-      <c r="B9" s="67" t="n">
+      <c r="B9" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="67" t="n">
+      <c r="C9" s="69" t="n">
         <v>31</v>
       </c>
       <c r="J9" s="57">
@@ -13688,7 +13732,7 @@
           <t>No-Spend Days:</t>
         </is>
       </c>
-      <c r="B12" s="68">
+      <c r="B12" s="70">
         <f>IFERROR(COUNTIF(J5:P10,0)-COUNTIF(J5:P10,""),0)</f>
         <v/>
       </c>
@@ -15935,7 +15979,7 @@
           <t>Salary</t>
         </is>
       </c>
-      <c r="B35" s="69" t="inlineStr">
+      <c r="B35" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -15988,7 +16032,7 @@
         <f>IFERROR(VLOOKUP(A35,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O35" s="70">
+      <c r="O35" s="72">
         <f>IFERROR(VLOOKUP(A35,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -15999,7 +16043,7 @@
           <t>Partner Income</t>
         </is>
       </c>
-      <c r="B36" s="69" t="inlineStr">
+      <c r="B36" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16052,7 +16096,7 @@
         <f>IFERROR(VLOOKUP(A36,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O36" s="70">
+      <c r="O36" s="72">
         <f>IFERROR(VLOOKUP(A36,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16063,7 +16107,7 @@
           <t>Freelance</t>
         </is>
       </c>
-      <c r="B37" s="69" t="inlineStr">
+      <c r="B37" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16116,7 +16160,7 @@
         <f>IFERROR(VLOOKUP(A37,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O37" s="70">
+      <c r="O37" s="72">
         <f>IFERROR(VLOOKUP(A37,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16127,7 +16171,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="B38" s="69" t="inlineStr">
+      <c r="B38" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16180,7 +16224,7 @@
         <f>IFERROR(VLOOKUP(A38,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O38" s="70">
+      <c r="O38" s="72">
         <f>IFERROR(VLOOKUP(A38,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16191,7 +16235,7 @@
           <t>Investments</t>
         </is>
       </c>
-      <c r="B39" s="69" t="inlineStr">
+      <c r="B39" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16244,7 +16288,7 @@
         <f>IFERROR(VLOOKUP(A39,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O39" s="70">
+      <c r="O39" s="72">
         <f>IFERROR(VLOOKUP(A39,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16255,7 +16299,7 @@
           <t>Rental Income</t>
         </is>
       </c>
-      <c r="B40" s="69" t="inlineStr">
+      <c r="B40" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16308,7 +16352,7 @@
         <f>IFERROR(VLOOKUP(A40,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O40" s="70">
+      <c r="O40" s="72">
         <f>IFERROR(VLOOKUP(A40,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16319,7 +16363,7 @@
           <t>Refunds</t>
         </is>
       </c>
-      <c r="B41" s="69" t="inlineStr">
+      <c r="B41" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16372,7 +16416,7 @@
         <f>IFERROR(VLOOKUP(A41,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O41" s="70">
+      <c r="O41" s="72">
         <f>IFERROR(VLOOKUP(A41,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16383,7 +16427,7 @@
           <t>Other Income</t>
         </is>
       </c>
-      <c r="B42" s="69" t="inlineStr">
+      <c r="B42" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16436,7 +16480,7 @@
         <f>IFERROR(VLOOKUP(A42,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O42" s="70">
+      <c r="O42" s="72">
         <f>IFERROR(VLOOKUP(A42,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16447,7 +16491,7 @@
           <t>Rent/Mortgage</t>
         </is>
       </c>
-      <c r="B43" s="69" t="inlineStr">
+      <c r="B43" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16500,7 +16544,7 @@
         <f>IFERROR(VLOOKUP(A43,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O43" s="70">
+      <c r="O43" s="72">
         <f>IFERROR(VLOOKUP(A43,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16511,7 +16555,7 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B44" s="69" t="inlineStr">
+      <c r="B44" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16564,7 +16608,7 @@
         <f>IFERROR(VLOOKUP(A44,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O44" s="70">
+      <c r="O44" s="72">
         <f>IFERROR(VLOOKUP(A44,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16575,7 +16619,7 @@
           <t>Groceries</t>
         </is>
       </c>
-      <c r="B45" s="69" t="inlineStr">
+      <c r="B45" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16628,7 +16672,7 @@
         <f>IFERROR(VLOOKUP(A45,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O45" s="70">
+      <c r="O45" s="72">
         <f>IFERROR(VLOOKUP(A45,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16639,7 +16683,7 @@
           <t>Dining Out</t>
         </is>
       </c>
-      <c r="B46" s="69" t="inlineStr">
+      <c r="B46" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16692,7 +16736,7 @@
         <f>IFERROR(VLOOKUP(A46,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O46" s="70">
+      <c r="O46" s="72">
         <f>IFERROR(VLOOKUP(A46,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16703,7 +16747,7 @@
           <t>Transport</t>
         </is>
       </c>
-      <c r="B47" s="69" t="inlineStr">
+      <c r="B47" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16756,7 +16800,7 @@
         <f>IFERROR(VLOOKUP(A47,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O47" s="70">
+      <c r="O47" s="72">
         <f>IFERROR(VLOOKUP(A47,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16767,7 +16811,7 @@
           <t>Fuel</t>
         </is>
       </c>
-      <c r="B48" s="69" t="inlineStr">
+      <c r="B48" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16820,7 +16864,7 @@
         <f>IFERROR(VLOOKUP(A48,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O48" s="70">
+      <c r="O48" s="72">
         <f>IFERROR(VLOOKUP(A48,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16831,7 +16875,7 @@
           <t>Car/Auto</t>
         </is>
       </c>
-      <c r="B49" s="69" t="inlineStr">
+      <c r="B49" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16884,7 +16928,7 @@
         <f>IFERROR(VLOOKUP(A49,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O49" s="70">
+      <c r="O49" s="72">
         <f>IFERROR(VLOOKUP(A49,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16895,7 +16939,7 @@
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B50" s="69" t="inlineStr">
+      <c r="B50" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -16948,7 +16992,7 @@
         <f>IFERROR(VLOOKUP(A50,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O50" s="70">
+      <c r="O50" s="72">
         <f>IFERROR(VLOOKUP(A50,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -16959,7 +17003,7 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="B51" s="69" t="inlineStr">
+      <c r="B51" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17012,7 +17056,7 @@
         <f>IFERROR(VLOOKUP(A51,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O51" s="70">
+      <c r="O51" s="72">
         <f>IFERROR(VLOOKUP(A51,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17023,7 +17067,7 @@
           <t>Phone</t>
         </is>
       </c>
-      <c r="B52" s="69" t="inlineStr">
+      <c r="B52" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17076,7 +17120,7 @@
         <f>IFERROR(VLOOKUP(A52,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O52" s="70">
+      <c r="O52" s="72">
         <f>IFERROR(VLOOKUP(A52,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17087,7 +17131,7 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="B53" s="69" t="inlineStr">
+      <c r="B53" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17140,7 +17184,7 @@
         <f>IFERROR(VLOOKUP(A53,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O53" s="70">
+      <c r="O53" s="72">
         <f>IFERROR(VLOOKUP(A53,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17151,7 +17195,7 @@
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="B54" s="69" t="inlineStr">
+      <c r="B54" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17204,7 +17248,7 @@
         <f>IFERROR(VLOOKUP(A54,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O54" s="70">
+      <c r="O54" s="72">
         <f>IFERROR(VLOOKUP(A54,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17215,7 +17259,7 @@
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="B55" s="69" t="inlineStr">
+      <c r="B55" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17268,7 +17312,7 @@
         <f>IFERROR(VLOOKUP(A55,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O55" s="70">
+      <c r="O55" s="72">
         <f>IFERROR(VLOOKUP(A55,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17279,7 +17323,7 @@
           <t>Shopping</t>
         </is>
       </c>
-      <c r="B56" s="69" t="inlineStr">
+      <c r="B56" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17332,7 +17376,7 @@
         <f>IFERROR(VLOOKUP(A56,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O56" s="70">
+      <c r="O56" s="72">
         <f>IFERROR(VLOOKUP(A56,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17343,7 +17387,7 @@
           <t>Clothing</t>
         </is>
       </c>
-      <c r="B57" s="69" t="inlineStr">
+      <c r="B57" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17396,7 +17440,7 @@
         <f>IFERROR(VLOOKUP(A57,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O57" s="70">
+      <c r="O57" s="72">
         <f>IFERROR(VLOOKUP(A57,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17407,7 +17451,7 @@
           <t>Personal Care</t>
         </is>
       </c>
-      <c r="B58" s="69" t="inlineStr">
+      <c r="B58" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17460,7 +17504,7 @@
         <f>IFERROR(VLOOKUP(A58,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O58" s="70">
+      <c r="O58" s="72">
         <f>IFERROR(VLOOKUP(A58,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17471,7 +17515,7 @@
           <t>Gym/Fitness</t>
         </is>
       </c>
-      <c r="B59" s="69" t="inlineStr">
+      <c r="B59" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17524,7 +17568,7 @@
         <f>IFERROR(VLOOKUP(A59,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O59" s="70">
+      <c r="O59" s="72">
         <f>IFERROR(VLOOKUP(A59,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17535,7 +17579,7 @@
           <t>Pets</t>
         </is>
       </c>
-      <c r="B60" s="69" t="inlineStr">
+      <c r="B60" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17588,7 +17632,7 @@
         <f>IFERROR(VLOOKUP(A60,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O60" s="70">
+      <c r="O60" s="72">
         <f>IFERROR(VLOOKUP(A60,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17599,7 +17643,7 @@
           <t>Kids</t>
         </is>
       </c>
-      <c r="B61" s="69" t="inlineStr">
+      <c r="B61" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17652,7 +17696,7 @@
         <f>IFERROR(VLOOKUP(A61,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O61" s="70">
+      <c r="O61" s="72">
         <f>IFERROR(VLOOKUP(A61,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17663,7 +17707,7 @@
           <t>Gifts/Donations</t>
         </is>
       </c>
-      <c r="B62" s="69" t="inlineStr">
+      <c r="B62" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17716,7 +17760,7 @@
         <f>IFERROR(VLOOKUP(A62,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O62" s="70">
+      <c r="O62" s="72">
         <f>IFERROR(VLOOKUP(A62,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17727,7 +17771,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="B63" s="69" t="inlineStr">
+      <c r="B63" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17780,7 +17824,7 @@
         <f>IFERROR(VLOOKUP(A63,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O63" s="70">
+      <c r="O63" s="72">
         <f>IFERROR(VLOOKUP(A63,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
@@ -17791,7 +17835,7 @@
           <t>Miscellaneous</t>
         </is>
       </c>
-      <c r="B64" s="69" t="inlineStr">
+      <c r="B64" s="71" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
@@ -17844,7 +17888,7 @@
         <f>IFERROR(VLOOKUP(A64,Settings!$A$30:$C$59,3,FALSE),0)</f>
         <v/>
       </c>
-      <c r="O64" s="70">
+      <c r="O64" s="72">
         <f>IFERROR(VLOOKUP(A64,Settings!$A$30:$C$59,3,FALSE),0)*12</f>
         <v/>
       </c>
